--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$P$1:$P$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$P$1:$P$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="patientsex">'cv_sample'!$V$1:$V$3</definedName>
     <definedName name="patienttumortype">'cv_sample'!$K$1:$K$4</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="samplematerial">'cv_sample'!$H$1:$H$7</definedName>
     <definedName name="sampleorigin">'cv_sample'!$G$1:$G$7</definedName>
     <definedName name="sampletaxonname">'cv_sample'!$I$1:$I$2</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="624">
   <si>
     <t>alias</t>
   </si>
@@ -453,6 +453,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -543,6 +546,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1182,9 +1188,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1203,6 +1206,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1404,6 +1410,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1413,9 +1422,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1455,7 +1461,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1524,6 +1530,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1599,6 +1608,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1620,6 +1632,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1665,6 +1680,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1677,6 +1695,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1686,9 +1707,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1713,6 +1731,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1773,10 +1794,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2414,10 +2435,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2458,10 +2479,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2488,7 +2509,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2505,7 +2526,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2522,7 +2543,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2539,7 +2560,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2556,7 +2577,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2573,7 +2594,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2590,7 +2611,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2607,7 +2628,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2624,7 +2645,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2641,7 +2662,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2655,7 +2676,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2669,7 +2690,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2683,7 +2704,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2697,7 +2718,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2711,7 +2732,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2725,7 +2746,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2739,7 +2760,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2753,7 +2774,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2763,8 +2784,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2775,7 +2799,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2786,7 +2810,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2797,7 +2821,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2808,7 +2832,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2819,7 +2843,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2830,7 +2854,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2841,7 +2865,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2852,7 +2876,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2863,7 +2887,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2874,7 +2898,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2885,7 +2909,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2896,7 +2920,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2907,7 +2931,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2915,7 +2939,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2923,7 +2947,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2931,7 +2955,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2939,7 +2963,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2947,7 +2971,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2955,7 +2979,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2963,7 +2987,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2971,7 +2995,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2979,7 +3003,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2987,236 +3011,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3238,27 +3267,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3278,122 +3307,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3417,132 +3446,132 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -3575,1530 +3604,1555 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:V289"/>
+  <dimension ref="G1:V294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:22">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="V1" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" spans="7:22">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="U2" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="V2" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="7:22">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="U3" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="V3" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4" spans="7:22">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="7:22">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="7:22">
       <c r="G6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="7:22">
       <c r="G7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="7:22">
       <c r="P8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="7:22">
       <c r="P9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="7:22">
       <c r="P10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="7:22">
       <c r="P11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="7:22">
       <c r="P12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="7:22">
       <c r="P13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="7:22">
       <c r="P14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="7:22">
       <c r="P15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="7:22">
       <c r="P16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="16:16">
       <c r="P17" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="16:16">
       <c r="P18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="16:16">
       <c r="P19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="16:16">
       <c r="P20" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="16:16">
       <c r="P21" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="16:16">
       <c r="P22" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="16:16">
       <c r="P23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="16:16">
       <c r="P24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="16:16">
       <c r="P25" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="16:16">
       <c r="P26" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="16:16">
       <c r="P27" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="16:16">
       <c r="P28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="16:16">
       <c r="P29" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="16:16">
       <c r="P30" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="16:16">
       <c r="P31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="16:16">
       <c r="P32" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="16:16">
       <c r="P33" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="16:16">
       <c r="P34" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="16:16">
       <c r="P35" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="16:16">
       <c r="P36" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="16:16">
       <c r="P37" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="16:16">
       <c r="P38" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="16:16">
       <c r="P39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="16:16">
       <c r="P40" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="16:16">
       <c r="P41" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="16:16">
       <c r="P42" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43" spans="16:16">
       <c r="P43" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="16:16">
       <c r="P44" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="16:16">
       <c r="P45" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" spans="16:16">
       <c r="P46" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="16:16">
       <c r="P47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="16:16">
       <c r="P48" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="16:16">
       <c r="P49" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="16:16">
       <c r="P50" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" spans="16:16">
       <c r="P51" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="16:16">
       <c r="P52" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="16:16">
       <c r="P53" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" spans="16:16">
       <c r="P54" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" spans="16:16">
       <c r="P55" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" spans="16:16">
       <c r="P56" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" spans="16:16">
       <c r="P57" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="58" spans="16:16">
       <c r="P58" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="16:16">
       <c r="P59" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="60" spans="16:16">
       <c r="P60" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="61" spans="16:16">
       <c r="P61" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="16:16">
       <c r="P62" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="16:16">
       <c r="P63" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="64" spans="16:16">
       <c r="P64" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="16:16">
       <c r="P65" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="16:16">
       <c r="P66" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="67" spans="16:16">
       <c r="P67" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="16:16">
       <c r="P68" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="69" spans="16:16">
       <c r="P69" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="16:16">
       <c r="P70" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="16:16">
       <c r="P71" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="16:16">
       <c r="P72" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73" spans="16:16">
       <c r="P73" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="16:16">
       <c r="P74" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" spans="16:16">
       <c r="P75" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="16:16">
       <c r="P76" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="16:16">
       <c r="P77" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" spans="16:16">
       <c r="P78" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="79" spans="16:16">
       <c r="P79" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" spans="16:16">
       <c r="P80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="81" spans="16:16">
       <c r="P81" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="82" spans="16:16">
       <c r="P82" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="83" spans="16:16">
       <c r="P83" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="16:16">
       <c r="P84" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="16:16">
       <c r="P85" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="86" spans="16:16">
       <c r="P86" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="16:16">
       <c r="P87" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="88" spans="16:16">
       <c r="P88" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="89" spans="16:16">
       <c r="P89" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="16:16">
       <c r="P90" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="91" spans="16:16">
       <c r="P91" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="16:16">
       <c r="P92" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="16:16">
       <c r="P93" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="94" spans="16:16">
       <c r="P94" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="16:16">
       <c r="P95" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="96" spans="16:16">
       <c r="P96" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="97" spans="16:16">
       <c r="P97" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="98" spans="16:16">
       <c r="P98" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="99" spans="16:16">
       <c r="P99" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="100" spans="16:16">
       <c r="P100" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="101" spans="16:16">
       <c r="P101" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="16:16">
       <c r="P102" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="103" spans="16:16">
       <c r="P103" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="16:16">
       <c r="P104" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="16:16">
       <c r="P105" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="16:16">
       <c r="P106" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="107" spans="16:16">
       <c r="P107" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="108" spans="16:16">
       <c r="P108" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="109" spans="16:16">
       <c r="P109" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="16:16">
       <c r="P110" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111" spans="16:16">
       <c r="P111" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="112" spans="16:16">
       <c r="P112" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="113" spans="16:16">
       <c r="P113" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="114" spans="16:16">
       <c r="P114" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="115" spans="16:16">
       <c r="P115" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="116" spans="16:16">
       <c r="P116" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="117" spans="16:16">
       <c r="P117" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="118" spans="16:16">
       <c r="P118" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="119" spans="16:16">
       <c r="P119" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="120" spans="16:16">
       <c r="P120" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="121" spans="16:16">
       <c r="P121" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="122" spans="16:16">
       <c r="P122" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="123" spans="16:16">
       <c r="P123" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="124" spans="16:16">
       <c r="P124" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="125" spans="16:16">
       <c r="P125" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="126" spans="16:16">
       <c r="P126" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="127" spans="16:16">
       <c r="P127" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="128" spans="16:16">
       <c r="P128" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="129" spans="16:16">
       <c r="P129" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="130" spans="16:16">
       <c r="P130" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="131" spans="16:16">
       <c r="P131" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="132" spans="16:16">
       <c r="P132" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="133" spans="16:16">
       <c r="P133" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="134" spans="16:16">
       <c r="P134" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="135" spans="16:16">
       <c r="P135" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="136" spans="16:16">
       <c r="P136" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="137" spans="16:16">
       <c r="P137" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="138" spans="16:16">
       <c r="P138" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="139" spans="16:16">
       <c r="P139" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="140" spans="16:16">
       <c r="P140" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" spans="16:16">
       <c r="P141" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="142" spans="16:16">
       <c r="P142" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="143" spans="16:16">
       <c r="P143" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="144" spans="16:16">
       <c r="P144" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="145" spans="16:16">
       <c r="P145" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="146" spans="16:16">
       <c r="P146" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="147" spans="16:16">
       <c r="P147" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148" spans="16:16">
       <c r="P148" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="149" spans="16:16">
       <c r="P149" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="150" spans="16:16">
       <c r="P150" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="151" spans="16:16">
       <c r="P151" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="152" spans="16:16">
       <c r="P152" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="153" spans="16:16">
       <c r="P153" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="154" spans="16:16">
       <c r="P154" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="155" spans="16:16">
       <c r="P155" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="156" spans="16:16">
       <c r="P156" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="157" spans="16:16">
       <c r="P157" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="158" spans="16:16">
       <c r="P158" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="159" spans="16:16">
       <c r="P159" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="160" spans="16:16">
       <c r="P160" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="161" spans="16:16">
       <c r="P161" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="162" spans="16:16">
       <c r="P162" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="163" spans="16:16">
       <c r="P163" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="164" spans="16:16">
       <c r="P164" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="165" spans="16:16">
       <c r="P165" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="166" spans="16:16">
       <c r="P166" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="167" spans="16:16">
       <c r="P167" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="168" spans="16:16">
       <c r="P168" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="169" spans="16:16">
       <c r="P169" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="170" spans="16:16">
       <c r="P170" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="171" spans="16:16">
       <c r="P171" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="172" spans="16:16">
       <c r="P172" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="173" spans="16:16">
       <c r="P173" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="174" spans="16:16">
       <c r="P174" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="175" spans="16:16">
       <c r="P175" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="176" spans="16:16">
       <c r="P176" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="177" spans="16:16">
       <c r="P177" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="178" spans="16:16">
       <c r="P178" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="179" spans="16:16">
       <c r="P179" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="180" spans="16:16">
       <c r="P180" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="181" spans="16:16">
       <c r="P181" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="182" spans="16:16">
       <c r="P182" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="183" spans="16:16">
       <c r="P183" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="184" spans="16:16">
       <c r="P184" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="185" spans="16:16">
       <c r="P185" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="186" spans="16:16">
       <c r="P186" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="187" spans="16:16">
       <c r="P187" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="188" spans="16:16">
       <c r="P188" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="189" spans="16:16">
       <c r="P189" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="190" spans="16:16">
       <c r="P190" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="16:16">
       <c r="P191" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="192" spans="16:16">
       <c r="P192" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="193" spans="16:16">
       <c r="P193" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="194" spans="16:16">
       <c r="P194" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="195" spans="16:16">
       <c r="P195" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="196" spans="16:16">
       <c r="P196" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="197" spans="16:16">
       <c r="P197" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="198" spans="16:16">
       <c r="P198" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="199" spans="16:16">
       <c r="P199" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="200" spans="16:16">
       <c r="P200" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="201" spans="16:16">
       <c r="P201" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="202" spans="16:16">
       <c r="P202" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="203" spans="16:16">
       <c r="P203" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="204" spans="16:16">
       <c r="P204" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="205" spans="16:16">
       <c r="P205" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="206" spans="16:16">
       <c r="P206" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="207" spans="16:16">
       <c r="P207" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="208" spans="16:16">
       <c r="P208" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="209" spans="16:16">
       <c r="P209" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="210" spans="16:16">
       <c r="P210" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="211" spans="16:16">
       <c r="P211" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="212" spans="16:16">
       <c r="P212" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="213" spans="16:16">
       <c r="P213" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="214" spans="16:16">
       <c r="P214" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="215" spans="16:16">
       <c r="P215" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="216" spans="16:16">
       <c r="P216" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="217" spans="16:16">
       <c r="P217" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="218" spans="16:16">
       <c r="P218" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="219" spans="16:16">
       <c r="P219" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="220" spans="16:16">
       <c r="P220" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="221" spans="16:16">
       <c r="P221" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="222" spans="16:16">
       <c r="P222" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="223" spans="16:16">
       <c r="P223" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="224" spans="16:16">
       <c r="P224" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="225" spans="16:16">
       <c r="P225" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="226" spans="16:16">
       <c r="P226" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="227" spans="16:16">
       <c r="P227" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="228" spans="16:16">
       <c r="P228" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="229" spans="16:16">
       <c r="P229" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="230" spans="16:16">
       <c r="P230" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="231" spans="16:16">
       <c r="P231" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="232" spans="16:16">
       <c r="P232" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="233" spans="16:16">
       <c r="P233" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="234" spans="16:16">
       <c r="P234" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="235" spans="16:16">
       <c r="P235" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="236" spans="16:16">
       <c r="P236" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="237" spans="16:16">
       <c r="P237" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="238" spans="16:16">
       <c r="P238" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="239" spans="16:16">
       <c r="P239" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="240" spans="16:16">
       <c r="P240" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="241" spans="16:16">
       <c r="P241" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="242" spans="16:16">
       <c r="P242" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="243" spans="16:16">
       <c r="P243" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="244" spans="16:16">
       <c r="P244" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="245" spans="16:16">
       <c r="P245" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="246" spans="16:16">
       <c r="P246" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="247" spans="16:16">
       <c r="P247" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="248" spans="16:16">
       <c r="P248" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="249" spans="16:16">
       <c r="P249" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="250" spans="16:16">
       <c r="P250" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="251" spans="16:16">
       <c r="P251" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="252" spans="16:16">
       <c r="P252" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="253" spans="16:16">
       <c r="P253" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="254" spans="16:16">
       <c r="P254" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="255" spans="16:16">
       <c r="P255" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="256" spans="16:16">
       <c r="P256" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="257" spans="16:16">
       <c r="P257" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="258" spans="16:16">
       <c r="P258" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="259" spans="16:16">
       <c r="P259" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="260" spans="16:16">
       <c r="P260" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="261" spans="16:16">
       <c r="P261" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="262" spans="16:16">
       <c r="P262" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="263" spans="16:16">
       <c r="P263" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="264" spans="16:16">
       <c r="P264" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="265" spans="16:16">
       <c r="P265" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="266" spans="16:16">
       <c r="P266" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="267" spans="16:16">
       <c r="P267" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="268" spans="16:16">
       <c r="P268" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="269" spans="16:16">
       <c r="P269" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="270" spans="16:16">
       <c r="P270" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="271" spans="16:16">
       <c r="P271" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="272" spans="16:16">
       <c r="P272" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="273" spans="16:16">
       <c r="P273" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="274" spans="16:16">
       <c r="P274" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="275" spans="16:16">
       <c r="P275" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="276" spans="16:16">
       <c r="P276" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="277" spans="16:16">
       <c r="P277" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="278" spans="16:16">
       <c r="P278" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="279" spans="16:16">
       <c r="P279" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="280" spans="16:16">
       <c r="P280" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="281" spans="16:16">
       <c r="P281" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="282" spans="16:16">
       <c r="P282" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="283" spans="16:16">
       <c r="P283" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="284" spans="16:16">
       <c r="P284" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="285" spans="16:16">
       <c r="P285" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="286" spans="16:16">
       <c r="P286" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="287" spans="16:16">
       <c r="P287" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="288" spans="16:16">
       <c r="P288" t="s">
-        <v>280</v>
+        <v>599</v>
       </c>
     </row>
     <row r="289" spans="16:16">
       <c r="P289" t="s">
-        <v>597</v>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="290" spans="16:16">
+      <c r="P290" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="291" spans="16:16">
+      <c r="P291" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="292" spans="16:16">
+      <c r="P292" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="293" spans="16:16">
+      <c r="P293" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="16:16">
+      <c r="P294" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -18,26 +18,26 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$N$1:$N$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="patientsex">'cv_sample'!$T$1:$T$3</definedName>
-    <definedName name="patienttumortype">'cv_sample'!$I$1:$I$4</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="samplematerial">'cv_sample'!$F$1:$F$7</definedName>
-    <definedName name="sampleorigin">'cv_sample'!$E$1:$E$7</definedName>
-    <definedName name="sampletaxonname">'cv_sample'!$G$1:$G$2</definedName>
+    <definedName name="patientsex">'cv_sample'!$U$1:$U$3</definedName>
+    <definedName name="patienttumortype">'cv_sample'!$J$1:$J$4</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="samplematerial">'cv_sample'!$G$1:$G$7</definedName>
+    <definedName name="sampleorigin">'cv_sample'!$F$1:$F$7</definedName>
+    <definedName name="sampletaxonname">'cv_sample'!$H$1:$H$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="wasthePDXmodelhumanised">'cv_sample'!$S$1:$S$3</definedName>
+    <definedName name="wasthePDXmodelhumanised">'cv_sample'!$T$1:$T$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="622">
   <si>
     <t>alias</t>
   </si>
@@ -453,6 +453,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -543,6 +546,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -843,6 +849,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1170,9 +1182,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1191,6 +1200,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1392,6 +1404,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1401,9 +1416,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1443,7 +1455,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1512,6 +1524,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1587,6 +1602,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1608,6 +1626,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1653,6 +1674,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1665,6 +1689,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1674,9 +1701,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1701,6 +1725,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1761,10 +1788,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2402,10 +2429,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2446,10 +2473,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2476,7 +2503,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2493,7 +2520,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2510,7 +2537,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2527,7 +2554,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2544,7 +2571,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2561,7 +2588,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2578,7 +2605,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2595,7 +2622,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2612,7 +2639,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2629,7 +2656,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2643,7 +2670,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2657,7 +2684,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2671,7 +2698,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2685,7 +2712,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2699,7 +2726,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2713,7 +2740,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2727,7 +2754,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2741,7 +2768,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2751,8 +2778,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2763,7 +2793,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2774,7 +2804,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2785,7 +2815,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2796,7 +2826,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2807,7 +2837,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2818,7 +2848,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2829,7 +2859,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2840,7 +2870,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2851,7 +2881,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2862,7 +2892,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2873,7 +2903,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2884,7 +2914,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2895,7 +2925,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2903,7 +2933,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2911,7 +2941,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2919,7 +2949,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2927,7 +2957,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2935,7 +2965,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2943,7 +2973,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2951,7 +2981,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2959,7 +2989,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2967,7 +2997,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2975,236 +3005,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3226,27 +3261,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3266,122 +3301,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3391,13 +3426,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3405,143 +3440,149 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>594</v>
+        <v>308</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="150" customHeight="1">
+        <v>615</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>290</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>595</v>
+        <v>309</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>sampleorigin</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>samplematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>sampletaxonname</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>patienttumortype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3:S101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
       <formula1>wasthePDXmodelhumanised</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
       <formula1>patientsex</formula1>
     </dataValidation>
   </dataValidations>
@@ -3551,1530 +3592,1555 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:T289"/>
+  <dimension ref="F1:U294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:20">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
+    <row r="1" spans="6:21">
       <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O1" t="s">
+        <v>310</v>
+      </c>
+      <c r="T1" t="s">
+        <v>613</v>
+      </c>
+      <c r="U1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="2" spans="6:21">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O2" t="s">
+        <v>311</v>
+      </c>
+      <c r="T2" t="s">
+        <v>614</v>
+      </c>
+      <c r="U2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3" spans="6:21">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J3" t="s">
+        <v>299</v>
+      </c>
+      <c r="O3" t="s">
+        <v>312</v>
+      </c>
+      <c r="T3" t="s">
+        <v>600</v>
+      </c>
+      <c r="U3" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="4" spans="6:21">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G4" t="s">
+        <v>280</v>
+      </c>
+      <c r="J4" t="s">
+        <v>280</v>
+      </c>
+      <c r="O4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" spans="6:21">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" spans="6:21">
+      <c r="F6" t="s">
         <v>279</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G6" t="s">
         <v>287</v>
       </c>
-      <c r="I1" t="s">
-        <v>293</v>
-      </c>
-      <c r="N1" t="s">
-        <v>306</v>
-      </c>
-      <c r="S1" t="s">
-        <v>604</v>
-      </c>
-      <c r="T1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="2" spans="5:20">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="O6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="6:21">
+      <c r="F7" t="s">
         <v>280</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G7" t="s">
         <v>288</v>
       </c>
-      <c r="I2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N2" t="s">
-        <v>307</v>
-      </c>
-      <c r="S2" t="s">
-        <v>605</v>
-      </c>
-      <c r="T2" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="3" spans="5:20">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F3" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" t="s">
-        <v>295</v>
-      </c>
-      <c r="N3" t="s">
-        <v>308</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="O7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="6:21">
+      <c r="O8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" spans="6:21">
+      <c r="O9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="6:21">
+      <c r="O10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="6:21">
+      <c r="O11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12" spans="6:21">
+      <c r="O12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="6:21">
+      <c r="O13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="6:21">
+      <c r="O14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="6:21">
+      <c r="O15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="6:21">
+      <c r="O16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="15:15">
+      <c r="O17" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="15:15">
+      <c r="O18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="15:15">
+      <c r="O19" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="20" spans="15:15">
+      <c r="O20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="15:15">
+      <c r="O21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="15:15">
+      <c r="O22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="23" spans="15:15">
+      <c r="O23" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="15:15">
+      <c r="O24" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" spans="15:15">
+      <c r="O25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="15:15">
+      <c r="O26" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="27" spans="15:15">
+      <c r="O27" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="15:15">
+      <c r="O28" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="29" spans="15:15">
+      <c r="O29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="15:15">
+      <c r="O30" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="15:15">
+      <c r="O31" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="15:15">
+      <c r="O32" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="15:15">
+      <c r="O33" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="15:15">
+      <c r="O34" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="35" spans="15:15">
+      <c r="O35" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="36" spans="15:15">
+      <c r="O36" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="37" spans="15:15">
+      <c r="O37" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="38" spans="15:15">
+      <c r="O38" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="15:15">
+      <c r="O39" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="15:15">
+      <c r="O40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="41" spans="15:15">
+      <c r="O41" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="42" spans="15:15">
+      <c r="O42" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="43" spans="15:15">
+      <c r="O43" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="15:15">
+      <c r="O44" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="45" spans="15:15">
+      <c r="O45" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="46" spans="15:15">
+      <c r="O46" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" spans="15:15">
+      <c r="O47" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" spans="15:15">
+      <c r="O48" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="15:15">
+      <c r="O49" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="50" spans="15:15">
+      <c r="O50" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="51" spans="15:15">
+      <c r="O51" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="15:15">
+      <c r="O52" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="53" spans="15:15">
+      <c r="O53" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="54" spans="15:15">
+      <c r="O54" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="55" spans="15:15">
+      <c r="O55" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="56" spans="15:15">
+      <c r="O56" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="15:15">
+      <c r="O57" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="58" spans="15:15">
+      <c r="O58" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="59" spans="15:15">
+      <c r="O59" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="60" spans="15:15">
+      <c r="O60" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="61" spans="15:15">
+      <c r="O61" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="62" spans="15:15">
+      <c r="O62" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" spans="15:15">
+      <c r="O63" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="64" spans="15:15">
+      <c r="O64" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="15:15">
+      <c r="O65" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="66" spans="15:15">
+      <c r="O66" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="67" spans="15:15">
+      <c r="O67" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="68" spans="15:15">
+      <c r="O68" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="69" spans="15:15">
+      <c r="O69" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" spans="15:15">
+      <c r="O70" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="71" spans="15:15">
+      <c r="O71" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="72" spans="15:15">
+      <c r="O72" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="73" spans="15:15">
+      <c r="O73" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="74" spans="15:15">
+      <c r="O74" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="75" spans="15:15">
+      <c r="O75" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76" spans="15:15">
+      <c r="O76" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="77" spans="15:15">
+      <c r="O77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="78" spans="15:15">
+      <c r="O78" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="79" spans="15:15">
+      <c r="O79" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="80" spans="15:15">
+      <c r="O80" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="81" spans="15:15">
+      <c r="O81" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="82" spans="15:15">
+      <c r="O82" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" spans="15:15">
+      <c r="O83" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="84" spans="15:15">
+      <c r="O84" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="85" spans="15:15">
+      <c r="O85" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="86" spans="15:15">
+      <c r="O86" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="87" spans="15:15">
+      <c r="O87" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="88" spans="15:15">
+      <c r="O88" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="89" spans="15:15">
+      <c r="O89" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="90" spans="15:15">
+      <c r="O90" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="91" spans="15:15">
+      <c r="O91" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="92" spans="15:15">
+      <c r="O92" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="93" spans="15:15">
+      <c r="O93" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="94" spans="15:15">
+      <c r="O94" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="95" spans="15:15">
+      <c r="O95" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="96" spans="15:15">
+      <c r="O96" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="97" spans="15:15">
+      <c r="O97" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="98" spans="15:15">
+      <c r="O98" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="99" spans="15:15">
+      <c r="O99" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="100" spans="15:15">
+      <c r="O100" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="101" spans="15:15">
+      <c r="O101" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="102" spans="15:15">
+      <c r="O102" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="103" spans="15:15">
+      <c r="O103" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="104" spans="15:15">
+      <c r="O104" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="105" spans="15:15">
+      <c r="O105" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="106" spans="15:15">
+      <c r="O106" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="107" spans="15:15">
+      <c r="O107" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="108" spans="15:15">
+      <c r="O108" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="109" spans="15:15">
+      <c r="O109" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="110" spans="15:15">
+      <c r="O110" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="111" spans="15:15">
+      <c r="O111" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="112" spans="15:15">
+      <c r="O112" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="113" spans="15:15">
+      <c r="O113" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="114" spans="15:15">
+      <c r="O114" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="115" spans="15:15">
+      <c r="O115" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="116" spans="15:15">
+      <c r="O116" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="117" spans="15:15">
+      <c r="O117" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="118" spans="15:15">
+      <c r="O118" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="119" spans="15:15">
+      <c r="O119" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="120" spans="15:15">
+      <c r="O120" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="121" spans="15:15">
+      <c r="O121" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="122" spans="15:15">
+      <c r="O122" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="123" spans="15:15">
+      <c r="O123" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="124" spans="15:15">
+      <c r="O124" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="125" spans="15:15">
+      <c r="O125" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="126" spans="15:15">
+      <c r="O126" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="127" spans="15:15">
+      <c r="O127" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="128" spans="15:15">
+      <c r="O128" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="129" spans="15:15">
+      <c r="O129" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="130" spans="15:15">
+      <c r="O130" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="131" spans="15:15">
+      <c r="O131" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="132" spans="15:15">
+      <c r="O132" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="133" spans="15:15">
+      <c r="O133" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="134" spans="15:15">
+      <c r="O134" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="135" spans="15:15">
+      <c r="O135" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="136" spans="15:15">
+      <c r="O136" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="137" spans="15:15">
+      <c r="O137" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="138" spans="15:15">
+      <c r="O138" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="139" spans="15:15">
+      <c r="O139" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="140" spans="15:15">
+      <c r="O140" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="141" spans="15:15">
+      <c r="O141" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="142" spans="15:15">
+      <c r="O142" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="143" spans="15:15">
+      <c r="O143" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="144" spans="15:15">
+      <c r="O144" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="145" spans="15:15">
+      <c r="O145" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="146" spans="15:15">
+      <c r="O146" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="147" spans="15:15">
+      <c r="O147" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="148" spans="15:15">
+      <c r="O148" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="149" spans="15:15">
+      <c r="O149" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="150" spans="15:15">
+      <c r="O150" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="151" spans="15:15">
+      <c r="O151" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="152" spans="15:15">
+      <c r="O152" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="153" spans="15:15">
+      <c r="O153" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="154" spans="15:15">
+      <c r="O154" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="155" spans="15:15">
+      <c r="O155" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="156" spans="15:15">
+      <c r="O156" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="157" spans="15:15">
+      <c r="O157" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="158" spans="15:15">
+      <c r="O158" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="159" spans="15:15">
+      <c r="O159" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="160" spans="15:15">
+      <c r="O160" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="161" spans="15:15">
+      <c r="O161" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="162" spans="15:15">
+      <c r="O162" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="163" spans="15:15">
+      <c r="O163" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="164" spans="15:15">
+      <c r="O164" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="165" spans="15:15">
+      <c r="O165" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="166" spans="15:15">
+      <c r="O166" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="167" spans="15:15">
+      <c r="O167" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="168" spans="15:15">
+      <c r="O168" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="169" spans="15:15">
+      <c r="O169" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="170" spans="15:15">
+      <c r="O170" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="171" spans="15:15">
+      <c r="O171" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="172" spans="15:15">
+      <c r="O172" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="173" spans="15:15">
+      <c r="O173" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="174" spans="15:15">
+      <c r="O174" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="175" spans="15:15">
+      <c r="O175" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="176" spans="15:15">
+      <c r="O176" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="177" spans="15:15">
+      <c r="O177" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="178" spans="15:15">
+      <c r="O178" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="179" spans="15:15">
+      <c r="O179" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="180" spans="15:15">
+      <c r="O180" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="181" spans="15:15">
+      <c r="O181" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="182" spans="15:15">
+      <c r="O182" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="183" spans="15:15">
+      <c r="O183" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="184" spans="15:15">
+      <c r="O184" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="185" spans="15:15">
+      <c r="O185" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="186" spans="15:15">
+      <c r="O186" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="187" spans="15:15">
+      <c r="O187" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="188" spans="15:15">
+      <c r="O188" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="189" spans="15:15">
+      <c r="O189" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="190" spans="15:15">
+      <c r="O190" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="191" spans="15:15">
+      <c r="O191" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="192" spans="15:15">
+      <c r="O192" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="193" spans="15:15">
+      <c r="O193" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="194" spans="15:15">
+      <c r="O194" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="195" spans="15:15">
+      <c r="O195" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="196" spans="15:15">
+      <c r="O196" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="197" spans="15:15">
+      <c r="O197" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="198" spans="15:15">
+      <c r="O198" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="199" spans="15:15">
+      <c r="O199" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="200" spans="15:15">
+      <c r="O200" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="201" spans="15:15">
+      <c r="O201" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="202" spans="15:15">
+      <c r="O202" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="203" spans="15:15">
+      <c r="O203" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="204" spans="15:15">
+      <c r="O204" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="205" spans="15:15">
+      <c r="O205" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="206" spans="15:15">
+      <c r="O206" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="207" spans="15:15">
+      <c r="O207" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="208" spans="15:15">
+      <c r="O208" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="209" spans="15:15">
+      <c r="O209" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="210" spans="15:15">
+      <c r="O210" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="211" spans="15:15">
+      <c r="O211" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="212" spans="15:15">
+      <c r="O212" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="213" spans="15:15">
+      <c r="O213" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="214" spans="15:15">
+      <c r="O214" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="215" spans="15:15">
+      <c r="O215" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="216" spans="15:15">
+      <c r="O216" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="217" spans="15:15">
+      <c r="O217" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="218" spans="15:15">
+      <c r="O218" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="219" spans="15:15">
+      <c r="O219" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="220" spans="15:15">
+      <c r="O220" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="221" spans="15:15">
+      <c r="O221" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="222" spans="15:15">
+      <c r="O222" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="223" spans="15:15">
+      <c r="O223" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="224" spans="15:15">
+      <c r="O224" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="225" spans="15:15">
+      <c r="O225" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="226" spans="15:15">
+      <c r="O226" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="227" spans="15:15">
+      <c r="O227" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="228" spans="15:15">
+      <c r="O228" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="229" spans="15:15">
+      <c r="O229" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="230" spans="15:15">
+      <c r="O230" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="231" spans="15:15">
+      <c r="O231" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="232" spans="15:15">
+      <c r="O232" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="233" spans="15:15">
+      <c r="O233" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="234" spans="15:15">
+      <c r="O234" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="235" spans="15:15">
+      <c r="O235" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="236" spans="15:15">
+      <c r="O236" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="237" spans="15:15">
+      <c r="O237" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="238" spans="15:15">
+      <c r="O238" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="239" spans="15:15">
+      <c r="O239" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="240" spans="15:15">
+      <c r="O240" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="241" spans="15:15">
+      <c r="O241" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="242" spans="15:15">
+      <c r="O242" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="243" spans="15:15">
+      <c r="O243" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="244" spans="15:15">
+      <c r="O244" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="245" spans="15:15">
+      <c r="O245" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="246" spans="15:15">
+      <c r="O246" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="247" spans="15:15">
+      <c r="O247" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="248" spans="15:15">
+      <c r="O248" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="249" spans="15:15">
+      <c r="O249" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="250" spans="15:15">
+      <c r="O250" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="251" spans="15:15">
+      <c r="O251" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="252" spans="15:15">
+      <c r="O252" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="253" spans="15:15">
+      <c r="O253" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="254" spans="15:15">
+      <c r="O254" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="255" spans="15:15">
+      <c r="O255" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="256" spans="15:15">
+      <c r="O256" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="257" spans="15:15">
+      <c r="O257" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="258" spans="15:15">
+      <c r="O258" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="259" spans="15:15">
+      <c r="O259" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="260" spans="15:15">
+      <c r="O260" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="261" spans="15:15">
+      <c r="O261" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="262" spans="15:15">
+      <c r="O262" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="263" spans="15:15">
+      <c r="O263" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="264" spans="15:15">
+      <c r="O264" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="265" spans="15:15">
+      <c r="O265" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="266" spans="15:15">
+      <c r="O266" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="267" spans="15:15">
+      <c r="O267" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="268" spans="15:15">
+      <c r="O268" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="269" spans="15:15">
+      <c r="O269" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="270" spans="15:15">
+      <c r="O270" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="271" spans="15:15">
+      <c r="O271" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="272" spans="15:15">
+      <c r="O272" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="273" spans="15:15">
+      <c r="O273" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="274" spans="15:15">
+      <c r="O274" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="275" spans="15:15">
+      <c r="O275" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="276" spans="15:15">
+      <c r="O276" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="277" spans="15:15">
+      <c r="O277" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="278" spans="15:15">
+      <c r="O278" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="279" spans="15:15">
+      <c r="O279" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="280" spans="15:15">
+      <c r="O280" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="281" spans="15:15">
+      <c r="O281" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="282" spans="15:15">
+      <c r="O282" t="s">
         <v>591</v>
       </c>
-      <c r="T3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="4" spans="5:20">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F4" t="s">
-        <v>276</v>
-      </c>
-      <c r="I4" t="s">
-        <v>276</v>
-      </c>
-      <c r="N4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="5:20">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F5" t="s">
-        <v>282</v>
-      </c>
-      <c r="N5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="5:20">
-      <c r="E6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F6" t="s">
-        <v>283</v>
-      </c>
-      <c r="N6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="5:20">
-      <c r="E7" t="s">
-        <v>276</v>
-      </c>
-      <c r="F7" t="s">
-        <v>284</v>
-      </c>
-      <c r="N7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="8" spans="5:20">
-      <c r="N8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="5:20">
-      <c r="N9" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="10" spans="5:20">
-      <c r="N10" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="11" spans="5:20">
-      <c r="N11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="12" spans="5:20">
-      <c r="N12" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" spans="5:20">
-      <c r="N13" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="14" spans="5:20">
-      <c r="N14" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" spans="5:20">
-      <c r="N15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="16" spans="5:20">
-      <c r="N16" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17" spans="14:14">
-      <c r="N17" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="18" spans="14:14">
-      <c r="N18" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="19" spans="14:14">
-      <c r="N19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="20" spans="14:14">
-      <c r="N20" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="21" spans="14:14">
-      <c r="N21" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="22" spans="14:14">
-      <c r="N22" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="23" spans="14:14">
-      <c r="N23" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="24" spans="14:14">
-      <c r="N24" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="25" spans="14:14">
-      <c r="N25" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26" spans="14:14">
-      <c r="N26" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="27" spans="14:14">
-      <c r="N27" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="28" spans="14:14">
-      <c r="N28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="14:14">
-      <c r="N29" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="30" spans="14:14">
-      <c r="N30" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="31" spans="14:14">
-      <c r="N31" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="32" spans="14:14">
-      <c r="N32" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="14:14">
-      <c r="N33" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="34" spans="14:14">
-      <c r="N34" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="14:14">
-      <c r="N35" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="36" spans="14:14">
-      <c r="N36" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="37" spans="14:14">
-      <c r="N37" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="38" spans="14:14">
-      <c r="N38" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="39" spans="14:14">
-      <c r="N39" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="40" spans="14:14">
-      <c r="N40" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="41" spans="14:14">
-      <c r="N41" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="42" spans="14:14">
-      <c r="N42" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="43" spans="14:14">
-      <c r="N43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="44" spans="14:14">
-      <c r="N44" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="45" spans="14:14">
-      <c r="N45" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="46" spans="14:14">
-      <c r="N46" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="47" spans="14:14">
-      <c r="N47" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="48" spans="14:14">
-      <c r="N48" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="49" spans="14:14">
-      <c r="N49" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="50" spans="14:14">
-      <c r="N50" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="51" spans="14:14">
-      <c r="N51" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="52" spans="14:14">
-      <c r="N52" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="53" spans="14:14">
-      <c r="N53" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="54" spans="14:14">
-      <c r="N54" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="55" spans="14:14">
-      <c r="N55" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="56" spans="14:14">
-      <c r="N56" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="57" spans="14:14">
-      <c r="N57" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="58" spans="14:14">
-      <c r="N58" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="59" spans="14:14">
-      <c r="N59" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="60" spans="14:14">
-      <c r="N60" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="61" spans="14:14">
-      <c r="N61" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="62" spans="14:14">
-      <c r="N62" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="63" spans="14:14">
-      <c r="N63" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="64" spans="14:14">
-      <c r="N64" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="65" spans="14:14">
-      <c r="N65" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="66" spans="14:14">
-      <c r="N66" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="67" spans="14:14">
-      <c r="N67" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="68" spans="14:14">
-      <c r="N68" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="69" spans="14:14">
-      <c r="N69" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="70" spans="14:14">
-      <c r="N70" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="71" spans="14:14">
-      <c r="N71" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="72" spans="14:14">
-      <c r="N72" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="73" spans="14:14">
-      <c r="N73" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="74" spans="14:14">
-      <c r="N74" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="75" spans="14:14">
-      <c r="N75" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="76" spans="14:14">
-      <c r="N76" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="77" spans="14:14">
-      <c r="N77" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="78" spans="14:14">
-      <c r="N78" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="79" spans="14:14">
-      <c r="N79" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="80" spans="14:14">
-      <c r="N80" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="81" spans="14:14">
-      <c r="N81" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="82" spans="14:14">
-      <c r="N82" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="83" spans="14:14">
-      <c r="N83" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="84" spans="14:14">
-      <c r="N84" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="85" spans="14:14">
-      <c r="N85" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="86" spans="14:14">
-      <c r="N86" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="87" spans="14:14">
-      <c r="N87" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="88" spans="14:14">
-      <c r="N88" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="89" spans="14:14">
-      <c r="N89" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="90" spans="14:14">
-      <c r="N90" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="91" spans="14:14">
-      <c r="N91" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="92" spans="14:14">
-      <c r="N92" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="93" spans="14:14">
-      <c r="N93" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="94" spans="14:14">
-      <c r="N94" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="95" spans="14:14">
-      <c r="N95" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="96" spans="14:14">
-      <c r="N96" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="97" spans="14:14">
-      <c r="N97" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="98" spans="14:14">
-      <c r="N98" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="99" spans="14:14">
-      <c r="N99" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="100" spans="14:14">
-      <c r="N100" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="101" spans="14:14">
-      <c r="N101" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="102" spans="14:14">
-      <c r="N102" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="103" spans="14:14">
-      <c r="N103" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="104" spans="14:14">
-      <c r="N104" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="105" spans="14:14">
-      <c r="N105" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="106" spans="14:14">
-      <c r="N106" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="107" spans="14:14">
-      <c r="N107" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="108" spans="14:14">
-      <c r="N108" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="109" spans="14:14">
-      <c r="N109" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="110" spans="14:14">
-      <c r="N110" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="111" spans="14:14">
-      <c r="N111" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="112" spans="14:14">
-      <c r="N112" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="113" spans="14:14">
-      <c r="N113" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="114" spans="14:14">
-      <c r="N114" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="115" spans="14:14">
-      <c r="N115" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="116" spans="14:14">
-      <c r="N116" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="117" spans="14:14">
-      <c r="N117" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="118" spans="14:14">
-      <c r="N118" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="119" spans="14:14">
-      <c r="N119" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="120" spans="14:14">
-      <c r="N120" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="121" spans="14:14">
-      <c r="N121" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="122" spans="14:14">
-      <c r="N122" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="123" spans="14:14">
-      <c r="N123" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="124" spans="14:14">
-      <c r="N124" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="125" spans="14:14">
-      <c r="N125" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="126" spans="14:14">
-      <c r="N126" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="127" spans="14:14">
-      <c r="N127" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="128" spans="14:14">
-      <c r="N128" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="129" spans="14:14">
-      <c r="N129" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="130" spans="14:14">
-      <c r="N130" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="131" spans="14:14">
-      <c r="N131" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="132" spans="14:14">
-      <c r="N132" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="133" spans="14:14">
-      <c r="N133" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="134" spans="14:14">
-      <c r="N134" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="135" spans="14:14">
-      <c r="N135" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="136" spans="14:14">
-      <c r="N136" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="137" spans="14:14">
-      <c r="N137" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="138" spans="14:14">
-      <c r="N138" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="139" spans="14:14">
-      <c r="N139" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="140" spans="14:14">
-      <c r="N140" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="141" spans="14:14">
-      <c r="N141" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="142" spans="14:14">
-      <c r="N142" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="143" spans="14:14">
-      <c r="N143" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="144" spans="14:14">
-      <c r="N144" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="145" spans="14:14">
-      <c r="N145" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="146" spans="14:14">
-      <c r="N146" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="147" spans="14:14">
-      <c r="N147" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="148" spans="14:14">
-      <c r="N148" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="149" spans="14:14">
-      <c r="N149" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="150" spans="14:14">
-      <c r="N150" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="151" spans="14:14">
-      <c r="N151" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="152" spans="14:14">
-      <c r="N152" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="153" spans="14:14">
-      <c r="N153" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="154" spans="14:14">
-      <c r="N154" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="155" spans="14:14">
-      <c r="N155" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="156" spans="14:14">
-      <c r="N156" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="157" spans="14:14">
-      <c r="N157" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="158" spans="14:14">
-      <c r="N158" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="159" spans="14:14">
-      <c r="N159" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="160" spans="14:14">
-      <c r="N160" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="161" spans="14:14">
-      <c r="N161" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="162" spans="14:14">
-      <c r="N162" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="163" spans="14:14">
-      <c r="N163" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="164" spans="14:14">
-      <c r="N164" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="165" spans="14:14">
-      <c r="N165" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="166" spans="14:14">
-      <c r="N166" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="167" spans="14:14">
-      <c r="N167" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="168" spans="14:14">
-      <c r="N168" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="169" spans="14:14">
-      <c r="N169" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="170" spans="14:14">
-      <c r="N170" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="171" spans="14:14">
-      <c r="N171" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="172" spans="14:14">
-      <c r="N172" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="173" spans="14:14">
-      <c r="N173" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="174" spans="14:14">
-      <c r="N174" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="175" spans="14:14">
-      <c r="N175" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="176" spans="14:14">
-      <c r="N176" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="177" spans="14:14">
-      <c r="N177" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="178" spans="14:14">
-      <c r="N178" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="179" spans="14:14">
-      <c r="N179" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="180" spans="14:14">
-      <c r="N180" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="181" spans="14:14">
-      <c r="N181" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="182" spans="14:14">
-      <c r="N182" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="183" spans="14:14">
-      <c r="N183" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="184" spans="14:14">
-      <c r="N184" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="185" spans="14:14">
-      <c r="N185" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="186" spans="14:14">
-      <c r="N186" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="187" spans="14:14">
-      <c r="N187" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="188" spans="14:14">
-      <c r="N188" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="189" spans="14:14">
-      <c r="N189" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="190" spans="14:14">
-      <c r="N190" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="191" spans="14:14">
-      <c r="N191" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="192" spans="14:14">
-      <c r="N192" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="193" spans="14:14">
-      <c r="N193" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="194" spans="14:14">
-      <c r="N194" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="195" spans="14:14">
-      <c r="N195" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="196" spans="14:14">
-      <c r="N196" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="197" spans="14:14">
-      <c r="N197" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="198" spans="14:14">
-      <c r="N198" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="199" spans="14:14">
-      <c r="N199" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="200" spans="14:14">
-      <c r="N200" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="201" spans="14:14">
-      <c r="N201" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="202" spans="14:14">
-      <c r="N202" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="203" spans="14:14">
-      <c r="N203" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="204" spans="14:14">
-      <c r="N204" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="205" spans="14:14">
-      <c r="N205" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="206" spans="14:14">
-      <c r="N206" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="207" spans="14:14">
-      <c r="N207" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="208" spans="14:14">
-      <c r="N208" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="209" spans="14:14">
-      <c r="N209" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="210" spans="14:14">
-      <c r="N210" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="211" spans="14:14">
-      <c r="N211" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="212" spans="14:14">
-      <c r="N212" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="213" spans="14:14">
-      <c r="N213" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="214" spans="14:14">
-      <c r="N214" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="215" spans="14:14">
-      <c r="N215" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="216" spans="14:14">
-      <c r="N216" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="217" spans="14:14">
-      <c r="N217" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="218" spans="14:14">
-      <c r="N218" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="219" spans="14:14">
-      <c r="N219" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="220" spans="14:14">
-      <c r="N220" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="221" spans="14:14">
-      <c r="N221" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="222" spans="14:14">
-      <c r="N222" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="223" spans="14:14">
-      <c r="N223" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="224" spans="14:14">
-      <c r="N224" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="225" spans="14:14">
-      <c r="N225" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="226" spans="14:14">
-      <c r="N226" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="227" spans="14:14">
-      <c r="N227" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="228" spans="14:14">
-      <c r="N228" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="229" spans="14:14">
-      <c r="N229" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="230" spans="14:14">
-      <c r="N230" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="231" spans="14:14">
-      <c r="N231" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="232" spans="14:14">
-      <c r="N232" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="233" spans="14:14">
-      <c r="N233" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="234" spans="14:14">
-      <c r="N234" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="235" spans="14:14">
-      <c r="N235" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="236" spans="14:14">
-      <c r="N236" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="237" spans="14:14">
-      <c r="N237" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="238" spans="14:14">
-      <c r="N238" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="239" spans="14:14">
-      <c r="N239" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="240" spans="14:14">
-      <c r="N240" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="241" spans="14:14">
-      <c r="N241" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="242" spans="14:14">
-      <c r="N242" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="243" spans="14:14">
-      <c r="N243" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="244" spans="14:14">
-      <c r="N244" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="245" spans="14:14">
-      <c r="N245" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="246" spans="14:14">
-      <c r="N246" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="247" spans="14:14">
-      <c r="N247" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="248" spans="14:14">
-      <c r="N248" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="249" spans="14:14">
-      <c r="N249" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="250" spans="14:14">
-      <c r="N250" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="251" spans="14:14">
-      <c r="N251" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="252" spans="14:14">
-      <c r="N252" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="253" spans="14:14">
-      <c r="N253" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="254" spans="14:14">
-      <c r="N254" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="255" spans="14:14">
-      <c r="N255" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="256" spans="14:14">
-      <c r="N256" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="257" spans="14:14">
-      <c r="N257" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="258" spans="14:14">
-      <c r="N258" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="259" spans="14:14">
-      <c r="N259" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="260" spans="14:14">
-      <c r="N260" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="261" spans="14:14">
-      <c r="N261" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="262" spans="14:14">
-      <c r="N262" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="263" spans="14:14">
-      <c r="N263" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="264" spans="14:14">
-      <c r="N264" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="265" spans="14:14">
-      <c r="N265" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="266" spans="14:14">
-      <c r="N266" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="267" spans="14:14">
-      <c r="N267" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="268" spans="14:14">
-      <c r="N268" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="269" spans="14:14">
-      <c r="N269" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="270" spans="14:14">
-      <c r="N270" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="271" spans="14:14">
-      <c r="N271" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="272" spans="14:14">
-      <c r="N272" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="273" spans="14:14">
-      <c r="N273" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="274" spans="14:14">
-      <c r="N274" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="275" spans="14:14">
-      <c r="N275" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="276" spans="14:14">
-      <c r="N276" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="277" spans="14:14">
-      <c r="N277" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="278" spans="14:14">
-      <c r="N278" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="279" spans="14:14">
-      <c r="N279" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="280" spans="14:14">
-      <c r="N280" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="281" spans="14:14">
-      <c r="N281" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="282" spans="14:14">
-      <c r="N282" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="283" spans="14:14">
-      <c r="N283" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="284" spans="14:14">
-      <c r="N284" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="285" spans="14:14">
-      <c r="N285" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="286" spans="14:14">
-      <c r="N286" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="287" spans="14:14">
-      <c r="N287" t="s">
+    </row>
+    <row r="283" spans="15:15">
+      <c r="O283" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="288" spans="14:14">
-      <c r="N288" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="289" spans="14:14">
-      <c r="N289" t="s">
+    <row r="284" spans="15:15">
+      <c r="O284" t="s">
         <v>593</v>
+      </c>
+    </row>
+    <row r="285" spans="15:15">
+      <c r="O285" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="286" spans="15:15">
+      <c r="O286" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="287" spans="15:15">
+      <c r="O287" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="288" spans="15:15">
+      <c r="O288" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="289" spans="15:15">
+      <c r="O289" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -18,26 +18,26 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$P$1:$P$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="patientsex">'cv_sample'!$U$1:$U$3</definedName>
-    <definedName name="patienttumortype">'cv_sample'!$J$1:$J$4</definedName>
+    <definedName name="patientsex">'cv_sample'!$V$1:$V$3</definedName>
+    <definedName name="patienttumortype">'cv_sample'!$K$1:$K$4</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="samplematerial">'cv_sample'!$G$1:$G$7</definedName>
-    <definedName name="sampleorigin">'cv_sample'!$F$1:$F$7</definedName>
-    <definedName name="sampletaxonname">'cv_sample'!$H$1:$H$2</definedName>
+    <definedName name="samplematerial">'cv_sample'!$H$1:$H$7</definedName>
+    <definedName name="sampleorigin">'cv_sample'!$G$1:$G$7</definedName>
+    <definedName name="sampletaxonname">'cv_sample'!$I$1:$I$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="wasthePDXmodelhumanised">'cv_sample'!$T$1:$T$3</definedName>
+    <definedName name="wasthePDXmodelhumanised">'cv_sample'!$U$1:$U$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="624">
   <si>
     <t>alias</t>
   </si>
@@ -853,6 +853,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3426,13 +3432,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3449,19 +3455,19 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>295</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>302</v>
@@ -3476,7 +3482,7 @@
         <v>308</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>603</v>
+        <v>310</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>605</v>
@@ -3491,13 +3497,16 @@
         <v>611</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="150" customHeight="1">
+        <v>617</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3514,19 +3523,19 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>303</v>
@@ -3541,7 +3550,7 @@
         <v>309</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>604</v>
+        <v>311</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>606</v>
@@ -3556,33 +3565,36 @@
         <v>612</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>sampleorigin</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
       <formula1>samplematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
       <formula1>sampletaxonname</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>patienttumortype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
       <formula1>wasthePDXmodelhumanised</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3:U101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:V101">
       <formula1>patientsex</formula1>
     </dataValidation>
   </dataValidations>
@@ -3592,1555 +3604,1555 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:U294"/>
+  <dimension ref="G1:V294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:21">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
+    <row r="1" spans="7:22">
       <c r="G1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s">
-        <v>291</v>
-      </c>
-      <c r="J1" t="s">
-        <v>297</v>
-      </c>
-      <c r="O1" t="s">
-        <v>310</v>
-      </c>
-      <c r="T1" t="s">
-        <v>613</v>
+        <v>285</v>
+      </c>
+      <c r="I1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K1" t="s">
+        <v>299</v>
+      </c>
+      <c r="P1" t="s">
+        <v>312</v>
       </c>
       <c r="U1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="2" spans="6:21">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="V1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="2" spans="7:22">
       <c r="G2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O2" t="s">
-        <v>311</v>
-      </c>
-      <c r="T2" t="s">
-        <v>614</v>
+        <v>286</v>
+      </c>
+      <c r="I2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K2" t="s">
+        <v>300</v>
+      </c>
+      <c r="P2" t="s">
+        <v>313</v>
       </c>
       <c r="U2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="3" spans="6:21">
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="V2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="7:22">
       <c r="G3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J3" t="s">
-        <v>299</v>
-      </c>
-      <c r="O3" t="s">
-        <v>312</v>
-      </c>
-      <c r="T3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K3" t="s">
+        <v>301</v>
+      </c>
+      <c r="P3" t="s">
+        <v>314</v>
+      </c>
+      <c r="U3" t="s">
+        <v>602</v>
+      </c>
+      <c r="V3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="4" spans="7:22">
+      <c r="G4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" t="s">
+        <v>282</v>
+      </c>
+      <c r="P4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="7:22">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" t="s">
+        <v>288</v>
+      </c>
+      <c r="P5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="7:22">
+      <c r="G6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" t="s">
+        <v>289</v>
+      </c>
+      <c r="P6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="7:22">
+      <c r="G7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H7" t="s">
+        <v>290</v>
+      </c>
+      <c r="P7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="7:22">
+      <c r="P8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="7:22">
+      <c r="P9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="7:22">
+      <c r="P10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="7:22">
+      <c r="P11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" spans="7:22">
+      <c r="P12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="13" spans="7:22">
+      <c r="P13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="7:22">
+      <c r="P14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="7:22">
+      <c r="P15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="7:22">
+      <c r="P16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="16:16">
+      <c r="P17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18" spans="16:16">
+      <c r="P18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="16:16">
+      <c r="P19" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="16:16">
+      <c r="P20" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="21" spans="16:16">
+      <c r="P21" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="16:16">
+      <c r="P22" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" spans="16:16">
+      <c r="P23" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="24" spans="16:16">
+      <c r="P24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="25" spans="16:16">
+      <c r="P25" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="26" spans="16:16">
+      <c r="P26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="16:16">
+      <c r="P27" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="16:16">
+      <c r="P28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29" spans="16:16">
+      <c r="P29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="16:16">
+      <c r="P30" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="16:16">
+      <c r="P31" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="16:16">
+      <c r="P32" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="16:16">
+      <c r="P33" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="16:16">
+      <c r="P34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="16:16">
+      <c r="P35" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36" spans="16:16">
+      <c r="P36" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="16:16">
+      <c r="P37" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="38" spans="16:16">
+      <c r="P38" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="39" spans="16:16">
+      <c r="P39" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40" spans="16:16">
+      <c r="P40" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="16:16">
+      <c r="P41" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="42" spans="16:16">
+      <c r="P42" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="43" spans="16:16">
+      <c r="P43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="44" spans="16:16">
+      <c r="P44" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" spans="16:16">
+      <c r="P45" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="16:16">
+      <c r="P46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="16:16">
+      <c r="P47" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="48" spans="16:16">
+      <c r="P48" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49" spans="16:16">
+      <c r="P49" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="50" spans="16:16">
+      <c r="P50" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="51" spans="16:16">
+      <c r="P51" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="52" spans="16:16">
+      <c r="P52" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="53" spans="16:16">
+      <c r="P53" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="54" spans="16:16">
+      <c r="P54" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="55" spans="16:16">
+      <c r="P55" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="56" spans="16:16">
+      <c r="P56" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="16:16">
+      <c r="P57" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="58" spans="16:16">
+      <c r="P58" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="59" spans="16:16">
+      <c r="P59" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="60" spans="16:16">
+      <c r="P60" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="61" spans="16:16">
+      <c r="P61" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="62" spans="16:16">
+      <c r="P62" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="63" spans="16:16">
+      <c r="P63" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="64" spans="16:16">
+      <c r="P64" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="65" spans="16:16">
+      <c r="P65" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="66" spans="16:16">
+      <c r="P66" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="67" spans="16:16">
+      <c r="P67" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="68" spans="16:16">
+      <c r="P68" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="69" spans="16:16">
+      <c r="P69" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="70" spans="16:16">
+      <c r="P70" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="71" spans="16:16">
+      <c r="P71" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="72" spans="16:16">
+      <c r="P72" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="16:16">
+      <c r="P73" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="74" spans="16:16">
+      <c r="P74" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="75" spans="16:16">
+      <c r="P75" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="76" spans="16:16">
+      <c r="P76" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="77" spans="16:16">
+      <c r="P77" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="78" spans="16:16">
+      <c r="P78" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="79" spans="16:16">
+      <c r="P79" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="80" spans="16:16">
+      <c r="P80" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="81" spans="16:16">
+      <c r="P81" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="82" spans="16:16">
+      <c r="P82" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="83" spans="16:16">
+      <c r="P83" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="84" spans="16:16">
+      <c r="P84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="85" spans="16:16">
+      <c r="P85" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="86" spans="16:16">
+      <c r="P86" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="87" spans="16:16">
+      <c r="P87" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="88" spans="16:16">
+      <c r="P88" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="89" spans="16:16">
+      <c r="P89" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="90" spans="16:16">
+      <c r="P90" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="91" spans="16:16">
+      <c r="P91" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="92" spans="16:16">
+      <c r="P92" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93" spans="16:16">
+      <c r="P93" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="94" spans="16:16">
+      <c r="P94" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="95" spans="16:16">
+      <c r="P95" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="96" spans="16:16">
+      <c r="P96" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="97" spans="16:16">
+      <c r="P97" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" spans="16:16">
+      <c r="P98" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="99" spans="16:16">
+      <c r="P99" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="100" spans="16:16">
+      <c r="P100" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="101" spans="16:16">
+      <c r="P101" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="102" spans="16:16">
+      <c r="P102" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="103" spans="16:16">
+      <c r="P103" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="104" spans="16:16">
+      <c r="P104" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="105" spans="16:16">
+      <c r="P105" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="106" spans="16:16">
+      <c r="P106" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="107" spans="16:16">
+      <c r="P107" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="108" spans="16:16">
+      <c r="P108" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="109" spans="16:16">
+      <c r="P109" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="110" spans="16:16">
+      <c r="P110" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="111" spans="16:16">
+      <c r="P111" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="112" spans="16:16">
+      <c r="P112" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="113" spans="16:16">
+      <c r="P113" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="114" spans="16:16">
+      <c r="P114" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="115" spans="16:16">
+      <c r="P115" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="116" spans="16:16">
+      <c r="P116" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="117" spans="16:16">
+      <c r="P117" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="118" spans="16:16">
+      <c r="P118" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="119" spans="16:16">
+      <c r="P119" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="120" spans="16:16">
+      <c r="P120" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="121" spans="16:16">
+      <c r="P121" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="122" spans="16:16">
+      <c r="P122" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="123" spans="16:16">
+      <c r="P123" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="124" spans="16:16">
+      <c r="P124" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="125" spans="16:16">
+      <c r="P125" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="126" spans="16:16">
+      <c r="P126" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="127" spans="16:16">
+      <c r="P127" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="128" spans="16:16">
+      <c r="P128" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="129" spans="16:16">
+      <c r="P129" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="130" spans="16:16">
+      <c r="P130" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="131" spans="16:16">
+      <c r="P131" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="132" spans="16:16">
+      <c r="P132" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="133" spans="16:16">
+      <c r="P133" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="134" spans="16:16">
+      <c r="P134" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="135" spans="16:16">
+      <c r="P135" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="136" spans="16:16">
+      <c r="P136" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="137" spans="16:16">
+      <c r="P137" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="138" spans="16:16">
+      <c r="P138" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="139" spans="16:16">
+      <c r="P139" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="140" spans="16:16">
+      <c r="P140" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="141" spans="16:16">
+      <c r="P141" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="142" spans="16:16">
+      <c r="P142" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="143" spans="16:16">
+      <c r="P143" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="144" spans="16:16">
+      <c r="P144" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="145" spans="16:16">
+      <c r="P145" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="146" spans="16:16">
+      <c r="P146" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="147" spans="16:16">
+      <c r="P147" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="148" spans="16:16">
+      <c r="P148" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="149" spans="16:16">
+      <c r="P149" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="150" spans="16:16">
+      <c r="P150" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="151" spans="16:16">
+      <c r="P151" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="152" spans="16:16">
+      <c r="P152" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="153" spans="16:16">
+      <c r="P153" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="154" spans="16:16">
+      <c r="P154" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="155" spans="16:16">
+      <c r="P155" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="156" spans="16:16">
+      <c r="P156" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="157" spans="16:16">
+      <c r="P157" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="158" spans="16:16">
+      <c r="P158" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="159" spans="16:16">
+      <c r="P159" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="160" spans="16:16">
+      <c r="P160" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="161" spans="16:16">
+      <c r="P161" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="162" spans="16:16">
+      <c r="P162" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="163" spans="16:16">
+      <c r="P163" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="164" spans="16:16">
+      <c r="P164" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="165" spans="16:16">
+      <c r="P165" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="166" spans="16:16">
+      <c r="P166" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="167" spans="16:16">
+      <c r="P167" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="168" spans="16:16">
+      <c r="P168" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="169" spans="16:16">
+      <c r="P169" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="170" spans="16:16">
+      <c r="P170" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="171" spans="16:16">
+      <c r="P171" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="172" spans="16:16">
+      <c r="P172" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="173" spans="16:16">
+      <c r="P173" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="174" spans="16:16">
+      <c r="P174" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="175" spans="16:16">
+      <c r="P175" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="176" spans="16:16">
+      <c r="P176" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="177" spans="16:16">
+      <c r="P177" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="178" spans="16:16">
+      <c r="P178" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="179" spans="16:16">
+      <c r="P179" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="180" spans="16:16">
+      <c r="P180" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="181" spans="16:16">
+      <c r="P181" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="182" spans="16:16">
+      <c r="P182" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="183" spans="16:16">
+      <c r="P183" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="184" spans="16:16">
+      <c r="P184" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="185" spans="16:16">
+      <c r="P185" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="186" spans="16:16">
+      <c r="P186" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="187" spans="16:16">
+      <c r="P187" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="188" spans="16:16">
+      <c r="P188" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="189" spans="16:16">
+      <c r="P189" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="190" spans="16:16">
+      <c r="P190" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="191" spans="16:16">
+      <c r="P191" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="192" spans="16:16">
+      <c r="P192" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="193" spans="16:16">
+      <c r="P193" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="194" spans="16:16">
+      <c r="P194" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="195" spans="16:16">
+      <c r="P195" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="196" spans="16:16">
+      <c r="P196" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="197" spans="16:16">
+      <c r="P197" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="198" spans="16:16">
+      <c r="P198" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="199" spans="16:16">
+      <c r="P199" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="200" spans="16:16">
+      <c r="P200" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="201" spans="16:16">
+      <c r="P201" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="202" spans="16:16">
+      <c r="P202" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="203" spans="16:16">
+      <c r="P203" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="204" spans="16:16">
+      <c r="P204" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="205" spans="16:16">
+      <c r="P205" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="206" spans="16:16">
+      <c r="P206" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="207" spans="16:16">
+      <c r="P207" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="208" spans="16:16">
+      <c r="P208" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="209" spans="16:16">
+      <c r="P209" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="210" spans="16:16">
+      <c r="P210" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="211" spans="16:16">
+      <c r="P211" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="212" spans="16:16">
+      <c r="P212" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="213" spans="16:16">
+      <c r="P213" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="214" spans="16:16">
+      <c r="P214" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="215" spans="16:16">
+      <c r="P215" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="216" spans="16:16">
+      <c r="P216" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="217" spans="16:16">
+      <c r="P217" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="218" spans="16:16">
+      <c r="P218" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="219" spans="16:16">
+      <c r="P219" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="220" spans="16:16">
+      <c r="P220" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="221" spans="16:16">
+      <c r="P221" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="222" spans="16:16">
+      <c r="P222" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="223" spans="16:16">
+      <c r="P223" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="224" spans="16:16">
+      <c r="P224" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="225" spans="16:16">
+      <c r="P225" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="226" spans="16:16">
+      <c r="P226" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="227" spans="16:16">
+      <c r="P227" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="228" spans="16:16">
+      <c r="P228" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="229" spans="16:16">
+      <c r="P229" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="230" spans="16:16">
+      <c r="P230" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="231" spans="16:16">
+      <c r="P231" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="232" spans="16:16">
+      <c r="P232" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="233" spans="16:16">
+      <c r="P233" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="234" spans="16:16">
+      <c r="P234" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="235" spans="16:16">
+      <c r="P235" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="236" spans="16:16">
+      <c r="P236" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="237" spans="16:16">
+      <c r="P237" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="238" spans="16:16">
+      <c r="P238" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="239" spans="16:16">
+      <c r="P239" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="240" spans="16:16">
+      <c r="P240" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="241" spans="16:16">
+      <c r="P241" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="242" spans="16:16">
+      <c r="P242" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="243" spans="16:16">
+      <c r="P243" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="244" spans="16:16">
+      <c r="P244" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="245" spans="16:16">
+      <c r="P245" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="246" spans="16:16">
+      <c r="P246" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="247" spans="16:16">
+      <c r="P247" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="248" spans="16:16">
+      <c r="P248" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="249" spans="16:16">
+      <c r="P249" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="250" spans="16:16">
+      <c r="P250" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="251" spans="16:16">
+      <c r="P251" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="252" spans="16:16">
+      <c r="P252" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="253" spans="16:16">
+      <c r="P253" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="254" spans="16:16">
+      <c r="P254" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="255" spans="16:16">
+      <c r="P255" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="256" spans="16:16">
+      <c r="P256" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="257" spans="16:16">
+      <c r="P257" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="258" spans="16:16">
+      <c r="P258" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="259" spans="16:16">
+      <c r="P259" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="260" spans="16:16">
+      <c r="P260" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="261" spans="16:16">
+      <c r="P261" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="262" spans="16:16">
+      <c r="P262" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="263" spans="16:16">
+      <c r="P263" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="264" spans="16:16">
+      <c r="P264" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="265" spans="16:16">
+      <c r="P265" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="266" spans="16:16">
+      <c r="P266" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="267" spans="16:16">
+      <c r="P267" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="268" spans="16:16">
+      <c r="P268" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="269" spans="16:16">
+      <c r="P269" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="270" spans="16:16">
+      <c r="P270" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="271" spans="16:16">
+      <c r="P271" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="272" spans="16:16">
+      <c r="P272" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="273" spans="16:16">
+      <c r="P273" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="274" spans="16:16">
+      <c r="P274" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="275" spans="16:16">
+      <c r="P275" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="276" spans="16:16">
+      <c r="P276" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="277" spans="16:16">
+      <c r="P277" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="278" spans="16:16">
+      <c r="P278" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="279" spans="16:16">
+      <c r="P279" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="280" spans="16:16">
+      <c r="P280" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="281" spans="16:16">
+      <c r="P281" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="282" spans="16:16">
+      <c r="P282" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="283" spans="16:16">
+      <c r="P283" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="284" spans="16:16">
+      <c r="P284" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="285" spans="16:16">
+      <c r="P285" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="286" spans="16:16">
+      <c r="P286" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="287" spans="16:16">
+      <c r="P287" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="288" spans="16:16">
+      <c r="P288" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="289" spans="16:16">
+      <c r="P289" t="s">
         <v>600</v>
       </c>
-      <c r="U3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="4" spans="6:21">
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
-      <c r="G4" t="s">
-        <v>280</v>
-      </c>
-      <c r="J4" t="s">
-        <v>280</v>
-      </c>
-      <c r="O4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="6:21">
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" t="s">
-        <v>286</v>
-      </c>
-      <c r="O5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="6:21">
-      <c r="F6" t="s">
-        <v>279</v>
-      </c>
-      <c r="G6" t="s">
-        <v>287</v>
-      </c>
-      <c r="O6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="6:21">
-      <c r="F7" t="s">
-        <v>280</v>
-      </c>
-      <c r="G7" t="s">
-        <v>288</v>
-      </c>
-      <c r="O7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="6:21">
-      <c r="O8" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="9" spans="6:21">
-      <c r="O9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="6:21">
-      <c r="O10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="11" spans="6:21">
-      <c r="O11" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="12" spans="6:21">
-      <c r="O12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="6:21">
-      <c r="O13" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="14" spans="6:21">
-      <c r="O14" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" spans="6:21">
-      <c r="O15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="6:21">
-      <c r="O16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="17" spans="15:15">
-      <c r="O17" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" spans="15:15">
-      <c r="O18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="19" spans="15:15">
-      <c r="O19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="15:15">
-      <c r="O20" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="21" spans="15:15">
-      <c r="O21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="15:15">
-      <c r="O22" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="23" spans="15:15">
-      <c r="O23" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="24" spans="15:15">
-      <c r="O24" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="25" spans="15:15">
-      <c r="O25" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="26" spans="15:15">
-      <c r="O26" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="27" spans="15:15">
-      <c r="O27" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" spans="15:15">
-      <c r="O28" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="29" spans="15:15">
-      <c r="O29" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="30" spans="15:15">
-      <c r="O30" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="31" spans="15:15">
-      <c r="O31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="32" spans="15:15">
-      <c r="O32" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="33" spans="15:15">
-      <c r="O33" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="34" spans="15:15">
-      <c r="O34" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="35" spans="15:15">
-      <c r="O35" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="36" spans="15:15">
-      <c r="O36" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="37" spans="15:15">
-      <c r="O37" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="38" spans="15:15">
-      <c r="O38" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="39" spans="15:15">
-      <c r="O39" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="40" spans="15:15">
-      <c r="O40" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="41" spans="15:15">
-      <c r="O41" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="42" spans="15:15">
-      <c r="O42" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="43" spans="15:15">
-      <c r="O43" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="44" spans="15:15">
-      <c r="O44" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="45" spans="15:15">
-      <c r="O45" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="46" spans="15:15">
-      <c r="O46" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="47" spans="15:15">
-      <c r="O47" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="48" spans="15:15">
-      <c r="O48" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="49" spans="15:15">
-      <c r="O49" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="50" spans="15:15">
-      <c r="O50" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="51" spans="15:15">
-      <c r="O51" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="52" spans="15:15">
-      <c r="O52" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="53" spans="15:15">
-      <c r="O53" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="54" spans="15:15">
-      <c r="O54" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="55" spans="15:15">
-      <c r="O55" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="56" spans="15:15">
-      <c r="O56" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="57" spans="15:15">
-      <c r="O57" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="58" spans="15:15">
-      <c r="O58" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="59" spans="15:15">
-      <c r="O59" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="60" spans="15:15">
-      <c r="O60" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="61" spans="15:15">
-      <c r="O61" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="62" spans="15:15">
-      <c r="O62" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="63" spans="15:15">
-      <c r="O63" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="64" spans="15:15">
-      <c r="O64" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="65" spans="15:15">
-      <c r="O65" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="66" spans="15:15">
-      <c r="O66" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="67" spans="15:15">
-      <c r="O67" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="68" spans="15:15">
-      <c r="O68" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="69" spans="15:15">
-      <c r="O69" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="70" spans="15:15">
-      <c r="O70" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="71" spans="15:15">
-      <c r="O71" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="72" spans="15:15">
-      <c r="O72" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="73" spans="15:15">
-      <c r="O73" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="74" spans="15:15">
-      <c r="O74" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="75" spans="15:15">
-      <c r="O75" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="76" spans="15:15">
-      <c r="O76" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="77" spans="15:15">
-      <c r="O77" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="78" spans="15:15">
-      <c r="O78" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="79" spans="15:15">
-      <c r="O79" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="80" spans="15:15">
-      <c r="O80" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="81" spans="15:15">
-      <c r="O81" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="82" spans="15:15">
-      <c r="O82" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="83" spans="15:15">
-      <c r="O83" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="84" spans="15:15">
-      <c r="O84" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="85" spans="15:15">
-      <c r="O85" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="86" spans="15:15">
-      <c r="O86" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="87" spans="15:15">
-      <c r="O87" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="88" spans="15:15">
-      <c r="O88" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="89" spans="15:15">
-      <c r="O89" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="90" spans="15:15">
-      <c r="O90" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="91" spans="15:15">
-      <c r="O91" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="92" spans="15:15">
-      <c r="O92" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="93" spans="15:15">
-      <c r="O93" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="94" spans="15:15">
-      <c r="O94" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="95" spans="15:15">
-      <c r="O95" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="96" spans="15:15">
-      <c r="O96" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="97" spans="15:15">
-      <c r="O97" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="98" spans="15:15">
-      <c r="O98" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="99" spans="15:15">
-      <c r="O99" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="100" spans="15:15">
-      <c r="O100" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="101" spans="15:15">
-      <c r="O101" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="102" spans="15:15">
-      <c r="O102" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="103" spans="15:15">
-      <c r="O103" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="104" spans="15:15">
-      <c r="O104" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="105" spans="15:15">
-      <c r="O105" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="106" spans="15:15">
-      <c r="O106" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="107" spans="15:15">
-      <c r="O107" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="108" spans="15:15">
-      <c r="O108" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="109" spans="15:15">
-      <c r="O109" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="110" spans="15:15">
-      <c r="O110" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="111" spans="15:15">
-      <c r="O111" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="112" spans="15:15">
-      <c r="O112" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="113" spans="15:15">
-      <c r="O113" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="114" spans="15:15">
-      <c r="O114" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="115" spans="15:15">
-      <c r="O115" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="116" spans="15:15">
-      <c r="O116" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="117" spans="15:15">
-      <c r="O117" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="118" spans="15:15">
-      <c r="O118" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="119" spans="15:15">
-      <c r="O119" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="120" spans="15:15">
-      <c r="O120" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="121" spans="15:15">
-      <c r="O121" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="122" spans="15:15">
-      <c r="O122" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="123" spans="15:15">
-      <c r="O123" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="124" spans="15:15">
-      <c r="O124" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="125" spans="15:15">
-      <c r="O125" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="126" spans="15:15">
-      <c r="O126" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="127" spans="15:15">
-      <c r="O127" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="128" spans="15:15">
-      <c r="O128" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="129" spans="15:15">
-      <c r="O129" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="130" spans="15:15">
-      <c r="O130" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="131" spans="15:15">
-      <c r="O131" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="132" spans="15:15">
-      <c r="O132" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="133" spans="15:15">
-      <c r="O133" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="134" spans="15:15">
-      <c r="O134" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="135" spans="15:15">
-      <c r="O135" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="136" spans="15:15">
-      <c r="O136" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="137" spans="15:15">
-      <c r="O137" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="138" spans="15:15">
-      <c r="O138" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="139" spans="15:15">
-      <c r="O139" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="140" spans="15:15">
-      <c r="O140" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="141" spans="15:15">
-      <c r="O141" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="142" spans="15:15">
-      <c r="O142" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="143" spans="15:15">
-      <c r="O143" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="144" spans="15:15">
-      <c r="O144" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="145" spans="15:15">
-      <c r="O145" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="146" spans="15:15">
-      <c r="O146" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="147" spans="15:15">
-      <c r="O147" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="148" spans="15:15">
-      <c r="O148" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="149" spans="15:15">
-      <c r="O149" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="150" spans="15:15">
-      <c r="O150" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="151" spans="15:15">
-      <c r="O151" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="152" spans="15:15">
-      <c r="O152" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="153" spans="15:15">
-      <c r="O153" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="154" spans="15:15">
-      <c r="O154" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="155" spans="15:15">
-      <c r="O155" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="156" spans="15:15">
-      <c r="O156" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="157" spans="15:15">
-      <c r="O157" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="158" spans="15:15">
-      <c r="O158" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="159" spans="15:15">
-      <c r="O159" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="160" spans="15:15">
-      <c r="O160" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="161" spans="15:15">
-      <c r="O161" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="162" spans="15:15">
-      <c r="O162" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="163" spans="15:15">
-      <c r="O163" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="164" spans="15:15">
-      <c r="O164" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="165" spans="15:15">
-      <c r="O165" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="166" spans="15:15">
-      <c r="O166" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="167" spans="15:15">
-      <c r="O167" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="168" spans="15:15">
-      <c r="O168" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="169" spans="15:15">
-      <c r="O169" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="170" spans="15:15">
-      <c r="O170" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="171" spans="15:15">
-      <c r="O171" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="172" spans="15:15">
-      <c r="O172" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="173" spans="15:15">
-      <c r="O173" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="174" spans="15:15">
-      <c r="O174" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="175" spans="15:15">
-      <c r="O175" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="176" spans="15:15">
-      <c r="O176" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="177" spans="15:15">
-      <c r="O177" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="178" spans="15:15">
-      <c r="O178" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="179" spans="15:15">
-      <c r="O179" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="180" spans="15:15">
-      <c r="O180" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="181" spans="15:15">
-      <c r="O181" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="182" spans="15:15">
-      <c r="O182" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="183" spans="15:15">
-      <c r="O183" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="184" spans="15:15">
-      <c r="O184" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="185" spans="15:15">
-      <c r="O185" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="186" spans="15:15">
-      <c r="O186" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="187" spans="15:15">
-      <c r="O187" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="188" spans="15:15">
-      <c r="O188" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="189" spans="15:15">
-      <c r="O189" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="190" spans="15:15">
-      <c r="O190" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="191" spans="15:15">
-      <c r="O191" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="192" spans="15:15">
-      <c r="O192" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="193" spans="15:15">
-      <c r="O193" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="194" spans="15:15">
-      <c r="O194" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="195" spans="15:15">
-      <c r="O195" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="196" spans="15:15">
-      <c r="O196" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="197" spans="15:15">
-      <c r="O197" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="198" spans="15:15">
-      <c r="O198" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="199" spans="15:15">
-      <c r="O199" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="200" spans="15:15">
-      <c r="O200" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="201" spans="15:15">
-      <c r="O201" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="202" spans="15:15">
-      <c r="O202" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="203" spans="15:15">
-      <c r="O203" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="204" spans="15:15">
-      <c r="O204" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="205" spans="15:15">
-      <c r="O205" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="206" spans="15:15">
-      <c r="O206" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="207" spans="15:15">
-      <c r="O207" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="208" spans="15:15">
-      <c r="O208" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="209" spans="15:15">
-      <c r="O209" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="210" spans="15:15">
-      <c r="O210" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="211" spans="15:15">
-      <c r="O211" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="212" spans="15:15">
-      <c r="O212" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="213" spans="15:15">
-      <c r="O213" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="214" spans="15:15">
-      <c r="O214" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="215" spans="15:15">
-      <c r="O215" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="216" spans="15:15">
-      <c r="O216" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="217" spans="15:15">
-      <c r="O217" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="218" spans="15:15">
-      <c r="O218" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="219" spans="15:15">
-      <c r="O219" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="220" spans="15:15">
-      <c r="O220" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="221" spans="15:15">
-      <c r="O221" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="222" spans="15:15">
-      <c r="O222" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="223" spans="15:15">
-      <c r="O223" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="224" spans="15:15">
-      <c r="O224" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="225" spans="15:15">
-      <c r="O225" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="226" spans="15:15">
-      <c r="O226" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="227" spans="15:15">
-      <c r="O227" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="228" spans="15:15">
-      <c r="O228" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="229" spans="15:15">
-      <c r="O229" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="230" spans="15:15">
-      <c r="O230" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="231" spans="15:15">
-      <c r="O231" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="232" spans="15:15">
-      <c r="O232" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="233" spans="15:15">
-      <c r="O233" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="234" spans="15:15">
-      <c r="O234" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="235" spans="15:15">
-      <c r="O235" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="236" spans="15:15">
-      <c r="O236" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="237" spans="15:15">
-      <c r="O237" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="238" spans="15:15">
-      <c r="O238" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="239" spans="15:15">
-      <c r="O239" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="240" spans="15:15">
-      <c r="O240" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="241" spans="15:15">
-      <c r="O241" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="242" spans="15:15">
-      <c r="O242" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="243" spans="15:15">
-      <c r="O243" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="244" spans="15:15">
-      <c r="O244" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="245" spans="15:15">
-      <c r="O245" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="246" spans="15:15">
-      <c r="O246" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="247" spans="15:15">
-      <c r="O247" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="248" spans="15:15">
-      <c r="O248" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="249" spans="15:15">
-      <c r="O249" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="250" spans="15:15">
-      <c r="O250" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="251" spans="15:15">
-      <c r="O251" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="252" spans="15:15">
-      <c r="O252" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="253" spans="15:15">
-      <c r="O253" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="254" spans="15:15">
-      <c r="O254" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="255" spans="15:15">
-      <c r="O255" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="256" spans="15:15">
-      <c r="O256" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="257" spans="15:15">
-      <c r="O257" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="258" spans="15:15">
-      <c r="O258" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="259" spans="15:15">
-      <c r="O259" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="260" spans="15:15">
-      <c r="O260" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="261" spans="15:15">
-      <c r="O261" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="262" spans="15:15">
-      <c r="O262" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="263" spans="15:15">
-      <c r="O263" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="264" spans="15:15">
-      <c r="O264" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="265" spans="15:15">
-      <c r="O265" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="266" spans="15:15">
-      <c r="O266" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="267" spans="15:15">
-      <c r="O267" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="268" spans="15:15">
-      <c r="O268" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="269" spans="15:15">
-      <c r="O269" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="270" spans="15:15">
-      <c r="O270" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="271" spans="15:15">
-      <c r="O271" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="272" spans="15:15">
-      <c r="O272" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="273" spans="15:15">
-      <c r="O273" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="274" spans="15:15">
-      <c r="O274" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="275" spans="15:15">
-      <c r="O275" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="276" spans="15:15">
-      <c r="O276" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="277" spans="15:15">
-      <c r="O277" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="278" spans="15:15">
-      <c r="O278" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="279" spans="15:15">
-      <c r="O279" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="280" spans="15:15">
-      <c r="O280" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="281" spans="15:15">
-      <c r="O281" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="282" spans="15:15">
-      <c r="O282" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="283" spans="15:15">
-      <c r="O283" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="284" spans="15:15">
-      <c r="O284" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="285" spans="15:15">
-      <c r="O285" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="286" spans="15:15">
-      <c r="O286" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="287" spans="15:15">
-      <c r="O287" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="288" spans="15:15">
-      <c r="O288" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="289" spans="15:15">
-      <c r="O289" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="290" spans="15:15">
-      <c r="O290" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="291" spans="15:15">
-      <c r="O291" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="292" spans="15:15">
-      <c r="O292" t="s">
+    </row>
+    <row r="290" spans="16:16">
+      <c r="P290" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="293" spans="15:15">
-      <c r="O293" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="294" spans="15:15">
-      <c r="O294" t="s">
+    <row r="291" spans="16:16">
+      <c r="P291" t="s">
         <v>602</v>
+      </c>
+    </row>
+    <row r="292" spans="16:16">
+      <c r="P292" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="293" spans="16:16">
+      <c r="P293" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="16:16">
+      <c r="P294" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000051/metadata_template_ERC000051.xlsx
+++ b/templates/ERC000051/metadata_template_ERC000051.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$P$1:$P$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="625">
   <si>
     <t>alias</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2438,7 +2441,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2482,7 +2485,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2509,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3246,6 +3249,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3267,27 +3275,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3307,122 +3315,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3446,132 +3454,132 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
   </sheetData>
@@ -3609,1550 +3617,1550 @@
   <sheetData>
     <row r="1" spans="7:22">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="U1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="V1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="7:22">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="U2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="V2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="7:22">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="V3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="7:22">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="7:22">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="7:22">
       <c r="G6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="7:22">
       <c r="G7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="7:22">
       <c r="P8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="7:22">
       <c r="P9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="7:22">
       <c r="P10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="7:22">
       <c r="P11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="7:22">
       <c r="P12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="7:22">
       <c r="P13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="7:22">
       <c r="P14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="7:22">
       <c r="P15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="7:22">
       <c r="P16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="16:16">
       <c r="P17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="16:16">
       <c r="P18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="16:16">
       <c r="P19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="16:16">
       <c r="P20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="16:16">
       <c r="P21" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="16:16">
       <c r="P22" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" spans="16:16">
       <c r="P23" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="16:16">
       <c r="P24" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="16:16">
       <c r="P25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="16:16">
       <c r="P26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="16:16">
       <c r="P27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="16:16">
       <c r="P28" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="16:16">
       <c r="P29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="16:16">
       <c r="P30" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="16:16">
       <c r="P31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="16:16">
       <c r="P32" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" spans="16:16">
       <c r="P33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="16:16">
       <c r="P34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="16:16">
       <c r="P35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="16:16">
       <c r="P36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="16:16">
       <c r="P37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="16:16">
       <c r="P38" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="16:16">
       <c r="P39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="16:16">
       <c r="P40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="16:16">
       <c r="P41" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="16:16">
       <c r="P42" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" spans="16:16">
       <c r="P43" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="16:16">
       <c r="P44" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45" spans="16:16">
       <c r="P45" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="16:16">
       <c r="P46" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="47" spans="16:16">
       <c r="P47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" spans="16:16">
       <c r="P48" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="16:16">
       <c r="P49" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" spans="16:16">
       <c r="P50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="16:16">
       <c r="P51" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="16:16">
       <c r="P52" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="53" spans="16:16">
       <c r="P53" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="16:16">
       <c r="P54" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="16:16">
       <c r="P55" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="16:16">
       <c r="P56" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="16:16">
       <c r="P57" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="16:16">
       <c r="P58" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="16:16">
       <c r="P59" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="60" spans="16:16">
       <c r="P60" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="16:16">
       <c r="P61" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="16:16">
       <c r="P62" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="16:16">
       <c r="P63" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" spans="16:16">
       <c r="P64" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="16:16">
       <c r="P65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="16:16">
       <c r="P66" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67" spans="16:16">
       <c r="P67" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="16:16">
       <c r="P68" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="16:16">
       <c r="P69" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="70" spans="16:16">
       <c r="P70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="16:16">
       <c r="P71" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" spans="16:16">
       <c r="P72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="16:16">
       <c r="P73" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="16:16">
       <c r="P74" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="16:16">
       <c r="P75" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="16:16">
       <c r="P76" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="16:16">
       <c r="P77" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="16:16">
       <c r="P78" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="16:16">
       <c r="P79" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="80" spans="16:16">
       <c r="P80" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" spans="16:16">
       <c r="P81" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="82" spans="16:16">
       <c r="P82" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="83" spans="16:16">
       <c r="P83" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="84" spans="16:16">
       <c r="P84" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="85" spans="16:16">
       <c r="P85" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="16:16">
       <c r="P86" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" spans="16:16">
       <c r="P87" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="88" spans="16:16">
       <c r="P88" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="89" spans="16:16">
       <c r="P89" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="90" spans="16:16">
       <c r="P90" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" spans="16:16">
       <c r="P91" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="92" spans="16:16">
       <c r="P92" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="93" spans="16:16">
       <c r="P93" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="94" spans="16:16">
       <c r="P94" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="95" spans="16:16">
       <c r="P95" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="96" spans="16:16">
       <c r="P96" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="97" spans="16:16">
       <c r="P97" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="98" spans="16:16">
       <c r="P98" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="99" spans="16:16">
       <c r="P99" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="100" spans="16:16">
       <c r="P100" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="101" spans="16:16">
       <c r="P101" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102" spans="16:16">
       <c r="P102" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="103" spans="16:16">
       <c r="P103" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="104" spans="16:16">
       <c r="P104" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="105" spans="16:16">
       <c r="P105" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="106" spans="16:16">
       <c r="P106" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="107" spans="16:16">
       <c r="P107" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="108" spans="16:16">
       <c r="P108" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="16:16">
       <c r="P109" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="110" spans="16:16">
       <c r="P110" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="111" spans="16:16">
       <c r="P111" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="112" spans="16:16">
       <c r="P112" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="113" spans="16:16">
       <c r="P113" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="114" spans="16:16">
       <c r="P114" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="115" spans="16:16">
       <c r="P115" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="116" spans="16:16">
       <c r="P116" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="117" spans="16:16">
       <c r="P117" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118" spans="16:16">
       <c r="P118" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="119" spans="16:16">
       <c r="P119" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="120" spans="16:16">
       <c r="P120" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="121" spans="16:16">
       <c r="P121" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="122" spans="16:16">
       <c r="P122" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="123" spans="16:16">
       <c r="P123" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="124" spans="16:16">
       <c r="P124" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="125" spans="16:16">
       <c r="P125" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="126" spans="16:16">
       <c r="P126" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="127" spans="16:16">
       <c r="P127" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="128" spans="16:16">
       <c r="P128" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="129" spans="16:16">
       <c r="P129" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="130" spans="16:16">
       <c r="P130" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="131" spans="16:16">
       <c r="P131" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="132" spans="16:16">
       <c r="P132" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="133" spans="16:16">
       <c r="P133" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="134" spans="16:16">
       <c r="P134" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="135" spans="16:16">
       <c r="P135" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="136" spans="16:16">
       <c r="P136" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="137" spans="16:16">
       <c r="P137" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="138" spans="16:16">
       <c r="P138" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="139" spans="16:16">
       <c r="P139" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="140" spans="16:16">
       <c r="P140" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="141" spans="16:16">
       <c r="P141" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="142" spans="16:16">
       <c r="P142" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="143" spans="16:16">
       <c r="P143" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="144" spans="16:16">
       <c r="P144" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="145" spans="16:16">
       <c r="P145" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="146" spans="16:16">
       <c r="P146" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="16:16">
       <c r="P147" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="148" spans="16:16">
       <c r="P148" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="16:16">
       <c r="P149" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="150" spans="16:16">
       <c r="P150" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="151" spans="16:16">
       <c r="P151" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="152" spans="16:16">
       <c r="P152" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="153" spans="16:16">
       <c r="P153" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="16:16">
       <c r="P154" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="155" spans="16:16">
       <c r="P155" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="156" spans="16:16">
       <c r="P156" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="157" spans="16:16">
       <c r="P157" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="158" spans="16:16">
       <c r="P158" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="159" spans="16:16">
       <c r="P159" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="160" spans="16:16">
       <c r="P160" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="161" spans="16:16">
       <c r="P161" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="162" spans="16:16">
       <c r="P162" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="163" spans="16:16">
       <c r="P163" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="164" spans="16:16">
       <c r="P164" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="165" spans="16:16">
       <c r="P165" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="166" spans="16:16">
       <c r="P166" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="167" spans="16:16">
       <c r="P167" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="168" spans="16:16">
       <c r="P168" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="169" spans="16:16">
       <c r="P169" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="170" spans="16:16">
       <c r="P170" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="171" spans="16:16">
       <c r="P171" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="172" spans="16:16">
       <c r="P172" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="173" spans="16:16">
       <c r="P173" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="174" spans="16:16">
       <c r="P174" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="175" spans="16:16">
       <c r="P175" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="16:16">
       <c r="P176" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="177" spans="16:16">
       <c r="P177" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="178" spans="16:16">
       <c r="P178" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="179" spans="16:16">
       <c r="P179" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="180" spans="16:16">
       <c r="P180" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="181" spans="16:16">
       <c r="P181" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="182" spans="16:16">
       <c r="P182" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="183" spans="16:16">
       <c r="P183" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="184" spans="16:16">
       <c r="P184" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="185" spans="16:16">
       <c r="P185" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="186" spans="16:16">
       <c r="P186" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="187" spans="16:16">
       <c r="P187" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="188" spans="16:16">
       <c r="P188" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" spans="16:16">
       <c r="P189" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="190" spans="16:16">
       <c r="P190" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="191" spans="16:16">
       <c r="P191" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="192" spans="16:16">
       <c r="P192" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="16:16">
       <c r="P193" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="194" spans="16:16">
       <c r="P194" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="195" spans="16:16">
       <c r="P195" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="196" spans="16:16">
       <c r="P196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="197" spans="16:16">
       <c r="P197" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="198" spans="16:16">
       <c r="P198" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="199" spans="16:16">
       <c r="P199" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="200" spans="16:16">
       <c r="P200" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="201" spans="16:16">
       <c r="P201" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="202" spans="16:16">
       <c r="P202" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="203" spans="16:16">
       <c r="P203" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="204" spans="16:16">
       <c r="P204" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="205" spans="16:16">
       <c r="P205" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="206" spans="16:16">
       <c r="P206" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="207" spans="16:16">
       <c r="P207" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="208" spans="16:16">
       <c r="P208" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="209" spans="16:16">
       <c r="P209" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="210" spans="16:16">
       <c r="P210" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="211" spans="16:16">
       <c r="P211" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="212" spans="16:16">
       <c r="P212" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="213" spans="16:16">
       <c r="P213" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="214" spans="16:16">
       <c r="P214" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="215" spans="16:16">
       <c r="P215" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="216" spans="16:16">
       <c r="P216" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="217" spans="16:16">
       <c r="P217" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="218" spans="16:16">
       <c r="P218" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="219" spans="16:16">
       <c r="P219" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="220" spans="16:16">
       <c r="P220" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="221" spans="16:16">
       <c r="P221" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="222" spans="16:16">
       <c r="P222" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="223" spans="16:16">
       <c r="P223" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="224" spans="16:16">
       <c r="P224" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="225" spans="16:16">
       <c r="P225" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="16:16">
       <c r="P226" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="227" spans="16:16">
       <c r="P227" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="228" spans="16:16">
       <c r="P228" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="229" spans="16:16">
       <c r="P229" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="230" spans="16:16">
       <c r="P230" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="231" spans="16:16">
       <c r="P231" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="232" spans="16:16">
       <c r="P232" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="233" spans="16:16">
       <c r="P233" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="234" spans="16:16">
       <c r="P234" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="235" spans="16:16">
       <c r="P235" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="236" spans="16:16">
       <c r="P236" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="237" spans="16:16">
       <c r="P237" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="238" spans="16:16">
       <c r="P238" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="239" spans="16:16">
       <c r="P239" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="240" spans="16:16">
       <c r="P240" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="241" spans="16:16">
       <c r="P241" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="242" spans="16:16">
       <c r="P242" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="243" spans="16:16">
       <c r="P243" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="244" spans="16:16">
       <c r="P244" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="245" spans="16:16">
       <c r="P245" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="246" spans="16:16">
       <c r="P246" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="247" spans="16:16">
       <c r="P247" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="248" spans="16:16">
       <c r="P248" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="249" spans="16:16">
       <c r="P249" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="250" spans="16:16">
       <c r="P250" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="251" spans="16:16">
       <c r="P251" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="252" spans="16:16">
       <c r="P252" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="253" spans="16:16">
       <c r="P253" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="254" spans="16:16">
       <c r="P254" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="255" spans="16:16">
       <c r="P255" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="256" spans="16:16">
       <c r="P256" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="257" spans="16:16">
       <c r="P257" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="258" spans="16:16">
       <c r="P258" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="259" spans="16:16">
       <c r="P259" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="260" spans="16:16">
       <c r="P260" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="261" spans="16:16">
       <c r="P261" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="262" spans="16:16">
       <c r="P262" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="263" spans="16:16">
       <c r="P263" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="264" spans="16:16">
       <c r="P264" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="265" spans="16:16">
       <c r="P265" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="266" spans="16:16">
       <c r="P266" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="267" spans="16:16">
       <c r="P267" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="268" spans="16:16">
       <c r="P268" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="269" spans="16:16">
       <c r="P269" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="270" spans="16:16">
       <c r="P270" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="271" spans="16:16">
       <c r="P271" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="272" spans="16:16">
       <c r="P272" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="273" spans="16:16">
       <c r="P273" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="274" spans="16:16">
       <c r="P274" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="275" spans="16:16">
       <c r="P275" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="276" spans="16:16">
       <c r="P276" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="277" spans="16:16">
       <c r="P277" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="278" spans="16:16">
       <c r="P278" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="279" spans="16:16">
       <c r="P279" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="280" spans="16:16">
       <c r="P280" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="281" spans="16:16">
       <c r="P281" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="282" spans="16:16">
       <c r="P282" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="283" spans="16:16">
       <c r="P283" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="284" spans="16:16">
       <c r="P284" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="285" spans="16:16">
       <c r="P285" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="286" spans="16:16">
       <c r="P286" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="287" spans="16:16">
       <c r="P287" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="288" spans="16:16">
       <c r="P288" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="289" spans="16:16">
       <c r="P289" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="290" spans="16:16">
       <c r="P290" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="291" spans="16:16">
       <c r="P291" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="292" spans="16:16">
       <c r="P292" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="293" spans="16:16">
       <c r="P293" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="294" spans="16:16">
       <c r="P294" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
